--- a/training_evaluation_forms/010_youth_work_methods_training_survey--training_evaluation_forms.xlsx
+++ b/training_evaluation_forms/010_youth_work_methods_training_survey--training_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'age_range',_'label':_'age_range',_'hint':_none,_'type':_'select_multiple',_'options':_['18-24',_'25-34',_'35-44',_'45-54',_'55+']}</t>
+          <t>age_range</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'age_range', 'label': 'Age Range', 'hint': None, 'type': 'select_multiple', 'options': ['18-24', '25-34', '35-44', '45-54', '55+']}</t>
+          <t>Age Range</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'role_participating',_'label':_'role_participating',_'hint':_none,_'type':_'select_one',_'options':_['youth',_'trainer',_'trainer/youth']}</t>
+          <t>role_participating</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'role_participating', 'label': 'Role Participating', 'hint': None, 'type': 'select_one', 'options': ['Youth', 'Trainer', 'Trainer/Youth']}</t>
+          <t>Role Participating</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'training_level',_'label':_'training_level',_'hint':_none,_'type':_'select_one',_'options':_['beginner',_'intermediate',_'advanced']}</t>
+          <t>training_level</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'training_level', 'label': 'Training Level', 'hint': None, 'type': 'select_one', 'options': ['Beginner', 'Intermediate', 'Advanced']}</t>
+          <t>Training Level</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'years_training',_'label':_'years_training',_'hint':_none,_'type':_'integer',_'options':_[]}</t>
+          <t>years_training</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'years_training', 'label': 'Years Training', 'hint': None, 'type': 'integer', 'options': []}</t>
+          <t>Years Training</t>
         </is>
       </c>
     </row>
